--- a/Assets/Excel/Condition/ConditionData.xlsx
+++ b/Assets/Excel/Condition/ConditionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\Assets\Excel\Condition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6EAD7E-F350-4C3B-BCFB-C78A13652A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EFF63D-DB0F-4A7E-B49D-E3117EB051F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConditionAbility" sheetId="1" r:id="rId1"/>
@@ -499,13 +499,13 @@
         <v>15</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <v>3</v>
       </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
       <c r="F2">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -516,13 +516,13 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>40</v>
@@ -536,7 +536,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -562,10 +562,10 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -579,13 +579,13 @@
         <v>100</v>
       </c>
       <c r="D6">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>10</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
